--- a/output/pdf_financials_xlsx/LNR.xlsx
+++ b/output/pdf_financials_xlsx/LNR.xlsx
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>89.535</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>81.29600000000001</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>81.29600000000001</v>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>89.535</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>81.29600000000001</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>81.29600000000001</v>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>135.748</v>
+        <v>46.213</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>118.926</v>
+        <v>37.63</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>6.338</v>
@@ -3489,13 +3489,13 @@
         <v>40.879</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>47313</v>
+        <v>162960</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>40.588</v>
+        <v>116.758</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>47.313</v>
+        <v>162.96</v>
       </c>
       <c r="Q48" s="1" t="inlineStr">
         <is>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="R48" s="3" t="n">
-        <v>79.48099999999999</v>
+        <v>177.749</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>86.873</v>
+        <v>198.832</v>
       </c>
     </row>
     <row r="49">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -39216,7 +39216,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E293" s="5" t="n">

--- a/output/pdf_financials_xlsx/LNR.xlsx
+++ b/output/pdf_financials_xlsx/LNR.xlsx
@@ -2241,40 +2241,40 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>5.349</v>
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>5.034</v>
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.131</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2.557</v>
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2.259</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>9.18</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>8.574999999999999</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>27.311</v>
+        <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>25.819</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>38.834</v>
+        <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>41.864</v>
+        <v>0</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
@@ -2282,19 +2282,19 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>51.612</v>
+        <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>58.217</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>64.092</v>
+        <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>77.334</v>
+        <v>0</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>82.298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2309,37 +2309,37 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-71.435</v>
+        <v>-76.46899999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>123.222</v>
+        <v>120.091</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>128.364</v>
+        <v>125.807</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>190.442</v>
+        <v>188.183</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>294.319</v>
+        <v>290.559</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>435.074</v>
+        <v>425.894</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>589.362</v>
+        <v>580.787</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>700.0410000000001</v>
+        <v>672.73</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>718.377</v>
+        <v>692.558</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>798.385</v>
+        <v>759.551</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>606.271</v>
+        <v>564.407</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>562217.612</v>
+        <v>562166</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>621.3049999999999</v>
+        <v>563.088</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>767.903</v>
+        <v>703.811</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>553.472</v>
+        <v>476.138</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>883.528</v>
+        <v>801.23</v>
       </c>
     </row>
     <row r="30">
@@ -2374,37 +2374,37 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-4.262460394651264</v>
+        <v>-4.562834519753448</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.527700182982658</v>
+        <v>5.387244507267942</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>4.485985227743326</v>
+        <v>4.39662478223415</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5.910794007081456</v>
+        <v>5.840680882550119</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8.185785021175144</v>
+        <v>8.081209537840332</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>10.42952506268037</v>
+        <v>10.2094635557289</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>11.41632364478106</v>
+        <v>11.2502203411171</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.65650168243421</v>
+        <v>11.20174157917032</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>10.97352186480078</v>
+        <v>10.57912538352801</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>10.47669324993813</v>
+        <v>9.967099625724124</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>8.174487475703231</v>
+        <v>7.610025801496747</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -2412,19 +2412,19 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>8.601105288489046</v>
+        <v>8.600315700548942</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>7.846829801446366</v>
+        <v>7.111572736798885</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>7.889253356335603</v>
+        <v>7.230787344203522</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>5.230304756501168</v>
+        <v>4.499499245040314</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>8.635148347831322</v>
+        <v>7.830810014773601</v>
       </c>
     </row>
     <row r="31">
@@ -7635,34 +7635,34 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>5.028</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>10.869</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>2.718</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>7.514</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>22.758</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>7.73</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>7.939</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>13.204</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>13.035</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>25.159</v>
       </c>
       <c r="N112" s="1" t="inlineStr">
         <is>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>6.883</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>36.17</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>3.778</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>66.833</v>
       </c>
       <c r="S112" s="3" t="n">
-        <v>0</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="113">
@@ -45826,11 +45826,7 @@
           <t>Amortization of other intangible assets</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>AmortizationOfIntangibles</t>
-        </is>
-      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -48264,7 +48260,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -55558,11 +55558,7 @@
           <t>Amortization of other intangible assets</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>AmortizationOfIntangibles</t>
-        </is>
-      </c>
+      <c r="D457" t="inlineStr"/>
       <c r="E457" s="5" t="n">
         <v>5.349</v>
       </c>
